--- a/data/STD_VLD_260922_site_master_TF_std.xlsx
+++ b/data/STD_VLD_260922_site_master_TF_std.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seokjjeong\Desktop\N-SRM_Site-Code-Verification\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4696F63E-4846-4BFA-814A-0495E95E1291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{389A79FA-7589-40FC-84A4-B3DE37DFB58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="17880" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TF_std" sheetId="1" r:id="rId1"/>
